--- a/MIS_CRM_Analysis_Excel_File/MIS-crm-lead-analysis.xlsx
+++ b/MIS_CRM_Analysis_Excel_File/MIS-crm-lead-analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tech\Projects\Excel\crm lead analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tech\Projects\Excel\crm lead analysis\MIS_CRM_Analysis_Excel_File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2600DA57-AC6F-419D-A2CD-6C02CFB87496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DE31B7-0E3F-47B0-A737-CB047DAF8536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw CRM Dump" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8972" uniqueCount="1628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8973" uniqueCount="1629">
   <si>
     <t>Lead ID</t>
   </si>
@@ -4944,6 +4944,9 @@
   </si>
   <si>
     <t>Status vs Lead Source</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
 </sst>
 </file>
@@ -5926,6 +5929,38 @@
     <xf numFmtId="0" fontId="41" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="13" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="13" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5991,6 +6026,12 @@
     <xf numFmtId="0" fontId="33" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -6015,92 +6056,12 @@
     <xf numFmtId="0" fontId="42" fillId="27" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="17" fillId="13" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="17" fillId="13" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FDF0028C-19FC-4E27-AC2A-BC00617EBE48}"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6131,20 +6092,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -10736,7 +10683,7 @@
             <xdr:cNvPr id="2" name="Status">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10814,7 +10761,7 @@
             <xdr:cNvPr id="3" name="City">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10890,7 +10837,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10926,7 +10873,7 @@
         <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10962,7 +10909,7 @@
         <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10998,7 +10945,7 @@
         <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11034,7 +10981,7 @@
         <xdr:cNvPr id="9" name="Straight Connector 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11089,7 +11036,7 @@
         <xdr:cNvPr id="12" name="Straight Connector 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11144,7 +11091,7 @@
         <xdr:cNvPr id="14" name="Straight Connector 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11199,7 +11146,7 @@
         <xdr:cNvPr id="25" name="Straight Connector 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000019000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000019000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11254,7 +11201,7 @@
         <xdr:cNvPr id="27" name="Straight Connector 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00001B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11314,7 +11261,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -17440,7 +17387,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21B24398-9E80-4734-B61C-24441E54D88B}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Lead Source" colHeaderCaption="Lead Source">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21B24398-9E80-4734-B61C-24441E54D88B}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Lead Source" colHeaderCaption="Lead Source">
   <location ref="K29:L37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -17539,7 +17486,7 @@
     <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="0">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -17556,7 +17503,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAAA9618-C1D4-45B1-956F-7CC2F0CD5445}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status" colHeaderCaption="Lead Source">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAAA9618-C1D4-45B1-956F-7CC2F0CD5445}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status" colHeaderCaption="Lead Source">
   <location ref="K18:L24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -17649,7 +17596,7 @@
     <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="1">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -17666,7 +17613,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F3B9D49-92D9-4566-BE5D-DD2A5860D248}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Lead Source">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F3B9D49-92D9-4566-BE5D-DD2A5860D248}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Lead Source">
   <location ref="K3:Q14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -17791,7 +17738,7 @@
     <dataField name="Lead Source Vs City" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="11">
+    <format dxfId="2">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -17808,7 +17755,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C4BD05D-53FE-452F-AB86-9DF35BCA8C1A}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Lead Source">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C4BD05D-53FE-452F-AB86-9DF35BCA8C1A}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Lead Source">
   <location ref="A21:I35" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -17935,7 +17882,7 @@
     <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="12">
+    <format dxfId="3">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -17952,7 +17899,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2AE6040-D966-432E-93ED-5335F72967F7}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2AE6040-D966-432E-93ED-5335F72967F7}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="Status">
   <location ref="A3:G17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -18062,10 +18009,10 @@
     <dataField name="Count of Status" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="13">
+    <format dxfId="5">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -18088,125 +18035,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4D65842-9FA9-40F1-AAF3-FCF35EBE950A}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="Y5:Z13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{602D481F-4888-46B5-972C-75DBB87DFC26}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{602D481F-4888-46B5-972C-75DBB87DFC26}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="AH5:AI15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -18315,8 +18144,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31E788D7-40A0-40B2-A317-DA6B0660CE70}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31E788D7-40A0-40B2-A317-DA6B0660CE70}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Y18:AE32" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -18450,8 +18279,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63F87A7D-152C-4B09-B0D3-6D55A408A4DF}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63F87A7D-152C-4B09-B0D3-6D55A408A4DF}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="AC5:AD11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -18599,6 +18428,124 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4D65842-9FA9-40F1-AAF3-FCF35EBE950A}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="Y5:Z13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Lead Source" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Status" xr10:uid="{00B61D08-ABD8-4045-9401-657E2FA74DAB}" sourceName="Status">
   <pivotTables>
@@ -18655,7 +18602,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C87595D-82F3-446B-89E4-6167E343AA19}" name="Table1" displayName="Table1" ref="A1:J501" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C87595D-82F3-446B-89E4-6167E343AA19}" name="Table1" displayName="Table1" ref="A1:J501" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J501" xr:uid="{5C87595D-82F3-446B-89E4-6167E343AA19}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{C149B129-AE4D-4DD0-9641-07FBD4EF87BF}" name="Lead ID"/>
@@ -18663,7 +18610,7 @@
     <tableColumn id="3" xr3:uid="{7BA7FB96-DB65-4C8A-9A25-A8B41149054F}" name="Lead Source"/>
     <tableColumn id="4" xr3:uid="{D87AA976-B442-495C-9B6E-47BB706054D2}" name="Phone Number"/>
     <tableColumn id="5" xr3:uid="{48408B5D-907C-4098-B88B-B0DE9A939C87}" name="Email"/>
-    <tableColumn id="6" xr3:uid="{19C4F1A2-FDBC-4D39-BC2C-D2BFEA358B52}" name="Lead Date" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{19C4F1A2-FDBC-4D39-BC2C-D2BFEA358B52}" name="Lead Date" dataDxfId="7"/>
     <tableColumn id="7" xr3:uid="{56DF7A39-C11C-437F-A0C4-26D6F908230B}" name="Status"/>
     <tableColumn id="8" xr3:uid="{EC0B42EF-22F9-4263-9D97-6A3F3FDD463C}" name="City"/>
     <tableColumn id="9" xr3:uid="{AF14FE2D-0051-4A82-A5FB-0EEEB0A87D7A}" name="Follow-up Done"/>
@@ -49171,34 +49118,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="132" t="s">
         <v>1506</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
       <c r="L1"/>
       <c r="M1"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="133" t="s">
         <v>1505</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
       <c r="L2"/>
       <c r="M2"/>
     </row>
@@ -49207,83 +49154,83 @@
       <c r="M3"/>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="122" t="s">
+      <c r="A4" s="134" t="s">
         <v>1504</v>
       </c>
-      <c r="B4" s="122"/>
-      <c r="C4" s="123" t="s">
+      <c r="B4" s="134"/>
+      <c r="C4" s="135" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124" t="s">
+      <c r="D4" s="135"/>
+      <c r="E4" s="136" t="s">
         <v>1503</v>
       </c>
-      <c r="F4" s="124"/>
-      <c r="G4" s="125" t="s">
+      <c r="F4" s="136"/>
+      <c r="G4" s="137" t="s">
         <v>1502</v>
       </c>
-      <c r="H4" s="125"/>
-      <c r="I4" s="126" t="s">
+      <c r="H4" s="137"/>
+      <c r="I4" s="138" t="s">
         <v>1501</v>
       </c>
-      <c r="J4" s="126"/>
+      <c r="J4" s="138"/>
       <c r="L4"/>
       <c r="M4"/>
     </row>
     <row r="5" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="117">
+      <c r="A5" s="129">
         <f>COUNTA('Cleaned Data'!G2:G501)</f>
         <v>500</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="118">
+      <c r="B5" s="129"/>
+      <c r="C5" s="130">
         <f>COUNTIF('Cleaned Data'!G1:G505,"Converted")</f>
         <v>184</v>
       </c>
-      <c r="D5" s="119"/>
-      <c r="E5" s="127">
+      <c r="D5" s="131"/>
+      <c r="E5" s="139">
         <f>C5/A5</f>
         <v>0.36799999999999999</v>
       </c>
-      <c r="F5" s="127"/>
-      <c r="G5" s="128">
+      <c r="F5" s="139"/>
+      <c r="G5" s="140">
         <f>COUNTIFS('Cleaned Data'!G1:G501,"Callback")+COUNTIFS('Cleaned Data'!G1:G501,"Open")</f>
         <v>195</v>
       </c>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128">
+      <c r="H5" s="140"/>
+      <c r="I5" s="140">
         <f>COUNTIFS('Cleaned Data'!G1:G501,"Lost")+COUNTIFS('Cleaned Data'!G1:G501,"Not interested")</f>
         <v>121</v>
       </c>
-      <c r="J5" s="128"/>
+      <c r="J5" s="140"/>
       <c r="L5"/>
       <c r="M5"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="108"/>
-      <c r="B6" s="108"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
+      <c r="A6" s="120"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="123"/>
+      <c r="J6" s="123"/>
       <c r="L6"/>
       <c r="M6"/>
     </row>
     <row r="7" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
+      <c r="A7" s="120"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
       <c r="L7"/>
       <c r="M7"/>
     </row>
@@ -49292,19 +49239,19 @@
       <c r="M8"/>
     </row>
     <row r="9" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="117" t="s">
         <v>1500</v>
       </c>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="112" t="s">
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="124" t="s">
         <v>1499</v>
       </c>
-      <c r="G9" s="113"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="114"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="126"/>
       <c r="J9"/>
       <c r="L9"/>
       <c r="M9"/>
@@ -49586,17 +49533,17 @@
     </row>
     <row r="19" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="105" t="s">
+      <c r="A20" s="117" t="s">
         <v>1488</v>
       </c>
-      <c r="B20" s="115"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="116"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="127"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="128"/>
       <c r="J20"/>
     </row>
     <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -50025,90 +49972,90 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="138" t="s">
+      <c r="A33" s="105" t="s">
         <v>153</v>
       </c>
-      <c r="B33" s="139">
+      <c r="B33" s="106">
         <f>COUNTIF('Cleaned Data'!$B$2:$B$501,A33)</f>
         <v>6</v>
       </c>
-      <c r="C33" s="139">
+      <c r="C33" s="106">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!C$21)</f>
         <v>3</v>
       </c>
-      <c r="D33" s="139">
+      <c r="D33" s="106">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!D$21)</f>
         <v>2</v>
       </c>
-      <c r="E33" s="139">
+      <c r="E33" s="106">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!E$21)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="139">
+      <c r="F33" s="106">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!F$21)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="139">
+      <c r="G33" s="106">
         <f>COUNTIFS('Cleaned Data'!$B$2:$B$501,Summary!$A33,'Cleaned Data'!$G$2:$G$501,Summary!G$21)</f>
         <v>1</v>
       </c>
-      <c r="H33" s="140">
+      <c r="H33" s="107">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="I33" s="141" t="s">
+      <c r="I33" s="108" t="s">
         <v>1475</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="142" t="s">
+      <c r="A34" s="109" t="s">
         <v>1468</v>
       </c>
-      <c r="B34" s="143">
+      <c r="B34" s="110">
         <f>SUM(B22:B33)</f>
         <v>500</v>
       </c>
-      <c r="C34" s="143">
+      <c r="C34" s="110">
         <f t="shared" ref="C34:G34" si="3">SUM(C22:C33)</f>
         <v>184</v>
       </c>
-      <c r="D34" s="143">
+      <c r="D34" s="110">
         <f t="shared" si="3"/>
         <v>134</v>
       </c>
-      <c r="E34" s="143">
+      <c r="E34" s="110">
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-      <c r="F34" s="143">
+      <c r="F34" s="110">
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-      <c r="G34" s="144">
+      <c r="G34" s="111">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="H34" s="146"/>
-      <c r="I34" s="145"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="112"/>
     </row>
     <row r="35" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="137"/>
+      <c r="A35" s="104"/>
     </row>
     <row r="36" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="118" t="s">
         <v>1474</v>
       </c>
-      <c r="B36" s="106"/>
-      <c r="C36" s="106"/>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="107" t="s">
+      <c r="B36" s="118"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="119" t="s">
         <v>1473</v>
       </c>
-      <c r="G36" s="107"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="107"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
     </row>
     <row r="37" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
@@ -50381,7 +50328,7 @@
     <mergeCell ref="C6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="D11:D15">
-    <cfRule type="expression" dxfId="14" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$C$11&gt;30</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50466,33 +50413,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="141" t="s">
         <v>1625</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
+      <c r="A2" s="141"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="147" t="s">
+      <c r="A3" s="114" t="s">
         <v>1618</v>
       </c>
       <c r="B3" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="147" t="s">
+      <c r="K3" s="114" t="s">
         <v>1624</v>
       </c>
       <c r="L3" s="89" t="s">
@@ -50503,7 +50450,7 @@
       <c r="A4" s="89" t="s">
         <v>1613</v>
       </c>
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="115" t="s">
         <v>54</v>
       </c>
       <c r="C4" s="63" t="s">
@@ -51043,10 +50990,10 @@
       <c r="G17" s="91">
         <v>500</v>
       </c>
-      <c r="K17" s="150" t="s">
+      <c r="K17" s="142" t="s">
         <v>1627</v>
       </c>
-      <c r="L17" s="150"/>
+      <c r="L17" s="142"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K18" s="89" t="s">
@@ -51073,7 +51020,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="147" t="s">
+      <c r="A21" s="114" t="s">
         <v>1615</v>
       </c>
       <c r="B21" s="89" t="s">
@@ -51290,10 +51237,10 @@
       <c r="I28" s="91">
         <v>44</v>
       </c>
-      <c r="K28" s="150" t="s">
+      <c r="K28" s="142" t="s">
         <v>1626</v>
       </c>
-      <c r="L28" s="150"/>
+      <c r="L28" s="142"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="90" t="s">
@@ -51557,16 +51504,17 @@
     <col min="1" max="19" width="8.88671875" style="63"/>
     <col min="20" max="20" width="7.5546875" style="63" customWidth="1"/>
     <col min="21" max="24" width="8.88671875" style="63"/>
-    <col min="25" max="25" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="3" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="4" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="11.6640625" customWidth="1"/>
     <col min="37" max="37" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="12" bestFit="1" customWidth="1"/>
@@ -51580,71 +51528,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="63" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="132" t="s">
         <v>1620</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="132"/>
     </row>
     <row r="2" spans="1:39" s="63" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="120"/>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
+      <c r="A2" s="132"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
     </row>
     <row r="3" spans="1:39" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q3" s="100" t="s">
         <v>1621</v>
       </c>
-      <c r="R3" s="129" t="s">
+      <c r="R3" s="143" t="s">
         <v>1623</v>
       </c>
-      <c r="S3" s="130"/>
-      <c r="T3" s="130"/>
+      <c r="S3" s="144"/>
+      <c r="T3" s="144"/>
     </row>
     <row r="4" spans="1:39" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q4" s="101"/>
       <c r="R4" s="101"/>
-      <c r="S4" s="135"/>
+      <c r="S4" s="149"/>
       <c r="T4" s="101"/>
     </row>
     <row r="5" spans="1:39" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q5" s="102"/>
       <c r="R5" s="102"/>
-      <c r="S5" s="136"/>
+      <c r="S5" s="150"/>
       <c r="T5" s="102"/>
       <c r="Y5" s="89" t="s">
         <v>1613</v>
@@ -51668,11 +51616,11 @@
     </row>
     <row r="6" spans="1:39" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q6" s="103"/>
-      <c r="R6" s="131" t="s">
+      <c r="R6" s="145" t="s">
         <v>1622</v>
       </c>
-      <c r="S6" s="131"/>
-      <c r="T6" s="131"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
       <c r="Y6" s="90" t="s">
         <v>37</v>
       </c>
@@ -51694,16 +51642,16 @@
       <c r="AJ6" s="63"/>
     </row>
     <row r="7" spans="1:39" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="Q7" s="132">
+      <c r="Q7" s="146">
         <f>Summary!C5</f>
         <v>184</v>
       </c>
-      <c r="R7" s="132"/>
-      <c r="S7" s="133">
+      <c r="R7" s="146"/>
+      <c r="S7" s="147">
         <f>Q7/Summary!A5</f>
         <v>0.36799999999999999</v>
       </c>
-      <c r="T7" s="134"/>
+      <c r="T7" s="148"/>
       <c r="Y7" s="90" t="s">
         <v>45</v>
       </c>
@@ -51725,10 +51673,13 @@
       <c r="AJ7" s="63"/>
     </row>
     <row r="8" spans="1:39" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q8" s="132"/>
-      <c r="R8" s="132"/>
-      <c r="S8" s="133"/>
-      <c r="T8" s="134"/>
+      <c r="Q8" s="146"/>
+      <c r="R8" s="146"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="148"/>
+      <c r="W8" s="63" t="s">
+        <v>1628</v>
+      </c>
       <c r="Y8" s="90" t="s">
         <v>22</v>
       </c>
